--- a/data/trans_dic/P25A$preocupacion-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 16,6</t>
+          <t>5,08; 17,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 21,22</t>
+          <t>6,34; 20,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 22,52</t>
+          <t>6,03; 21,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,56</t>
+          <t>0,0; 18,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 21,64</t>
+          <t>3,82; 21,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 16,36</t>
+          <t>2,89; 17,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,66</t>
+          <t>5,07; 14,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,21</t>
+          <t>6,83; 18,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,03</t>
+          <t>5,66; 15,59</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 16,78</t>
+          <t>3,26; 17,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,46</t>
+          <t>3,59; 18,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 25,79</t>
+          <t>8,34; 26,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 34,85</t>
+          <t>5,42; 31,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 23,6</t>
+          <t>3,74; 22,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 14,13</t>
+          <t>1,47; 13,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 18,96</t>
+          <t>5,94; 18,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 16,07</t>
+          <t>5,68; 16,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,67</t>
+          <t>5,92; 18,19</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 16,23</t>
+          <t>5,06; 16,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,3</t>
+          <t>1,85; 8,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 16,14</t>
+          <t>4,96; 16,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,98</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 23,66</t>
+          <t>0,0; 22,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,23</t>
+          <t>0,0; 28,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 14,78</t>
+          <t>4,39; 14,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,22</t>
+          <t>2,66; 9,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 15,8</t>
+          <t>4,69; 15,54</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,66</t>
+          <t>4,21; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,36</t>
+          <t>4,55; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 16,4</t>
+          <t>7,72; 16,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,52</t>
+          <t>3,5; 13,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,39</t>
+          <t>2,15; 11,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,49</t>
+          <t>4,06; 9,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,84</t>
+          <t>4,93; 10,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 13,55</t>
+          <t>6,81; 13,77</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 16,02</t>
+          <t>5,09; 16,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 21,65</t>
+          <t>8,19; 22,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 22,24</t>
+          <t>2,74; 22,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 14,32</t>
+          <t>1,35; 16,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 26,48</t>
+          <t>8,53; 27,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,39</t>
+          <t>2,04; 11,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,32</t>
+          <t>4,55; 12,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 21,42</t>
+          <t>9,38; 20,54</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,75</t>
+          <t>2,38; 21,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 19,72</t>
+          <t>2,09; 20,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 15,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,96</t>
+          <t>1,9; 18,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 18,95</t>
+          <t>1,97; 19,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 15,91</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,7</t>
+          <t>5,47; 9,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,94</t>
+          <t>5,93; 9,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,89</t>
+          <t>9,63; 14,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,65</t>
+          <t>4,89; 12,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,5</t>
+          <t>5,69; 11,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,69</t>
+          <t>5,69; 11,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,68</t>
+          <t>6,11; 9,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,62</t>
+          <t>6,2; 9,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,74</t>
+          <t>8,67; 12,91</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4811; 15916</t>
+          <t>4874; 16574</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6969; 23779</t>
+          <t>7108; 22974</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5717; 21024</t>
+          <t>5629; 20013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7065</t>
+          <t>0; 7135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1940; 11186</t>
+          <t>1973; 11300</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1732; 10042</t>
+          <t>1773; 10496</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6253; 19638</t>
+          <t>6795; 19654</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11352; 29828</t>
+          <t>11181; 29515</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8510; 24807</t>
+          <t>8766; 24125</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2131; 13396</t>
+          <t>2604; 13866</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3677; 15696</t>
+          <t>3225; 16898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5543; 18789</t>
+          <t>6073; 19559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3006; 14101</t>
+          <t>2192; 12670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1991; 12756</t>
+          <t>2022; 12225</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>991; 9458</t>
+          <t>985; 9366</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7655; 22812</t>
+          <t>7146; 22571</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7685; 23136</t>
+          <t>8181; 24287</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8332; 24701</t>
+          <t>8271; 25428</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4906; 17314</t>
+          <t>5397; 17629</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3074; 13452</t>
+          <t>2992; 14048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4754; 15858</t>
+          <t>4871; 16347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>972; 8322</t>
+          <t>0; 7982</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4646</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5895; 19372</t>
+          <t>5760; 18361</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5066; 18170</t>
+          <t>5248; 18553</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5357; 17609</t>
+          <t>5232; 17327</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11627; 28997</t>
+          <t>11447; 28786</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14698; 33054</t>
+          <t>14502; 32623</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17930; 37353</t>
+          <t>17572; 37791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8154</t>
+          <t>0; 8830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3955; 15299</t>
+          <t>3961; 15002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1838; 10742</t>
+          <t>1860; 9751</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13104; 31837</t>
+          <t>13603; 31584</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21491; 42497</t>
+          <t>21318; 43638</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21524; 42610</t>
+          <t>21427; 43310</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6197</t>
+          <t>0; 6136</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6647; 20364</t>
+          <t>6467; 20832</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9001; 23319</t>
+          <t>8815; 24533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>975; 7894</t>
+          <t>971; 8017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>943; 9945</t>
+          <t>939; 11650</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5698; 18591</t>
+          <t>5990; 19452</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2690; 12277</t>
+          <t>2024; 11207</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8489; 24224</t>
+          <t>8947; 25019</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17517; 38101</t>
+          <t>16681; 36538</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1460</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1589</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1181; 10163</t>
+          <t>1166; 10297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1305; 12018</t>
+          <t>1275; 12514</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5617</t>
+          <t>0; 5752</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1208; 10884</t>
+          <t>1038; 9881</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1828; 12691</t>
+          <t>1318; 12909</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6607</t>
+          <t>0; 6635</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34719; 60492</t>
+          <t>34141; 61047</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48967; 81135</t>
+          <t>48425; 80815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56644; 90187</t>
+          <t>58291; 90426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13204; 31723</t>
+          <t>12250; 30475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21878; 44199</t>
+          <t>21884; 44929</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18643; 39114</t>
+          <t>19026; 39638</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53454; 84654</t>
+          <t>53430; 85936</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>76367; 115511</t>
+          <t>74444; 114147</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>82202; 119729</t>
+          <t>81510; 121311</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$preocupacion-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 17,29</t>
+          <t>4,99; 17,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 20,5</t>
+          <t>6,55; 20,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 21,44</t>
+          <t>5,42; 20,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,74</t>
+          <t>0,0; 21,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 21,86</t>
+          <t>3,79; 20,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 17,1</t>
+          <t>2,86; 15,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 14,67</t>
+          <t>5,05; 15,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 18,02</t>
+          <t>7,11; 18,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 15,59</t>
+          <t>5,68; 15,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 17,37</t>
+          <t>3,38; 17,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 18,79</t>
+          <t>3,38; 17,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 26,85</t>
+          <t>7,46; 24,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 31,31</t>
+          <t>7,68; 32,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 22,61</t>
+          <t>3,71; 22,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,99</t>
+          <t>1,5; 14,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,76</t>
+          <t>6,01; 18,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,87</t>
+          <t>5,32; 16,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 18,19</t>
+          <t>5,98; 17,67</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 16,52</t>
+          <t>5,01; 16,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,67</t>
+          <t>1,97; 8,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 16,63</t>
+          <t>4,81; 16,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 20,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,69</t>
+          <t>2,62; 22,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,26</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,01</t>
+          <t>4,37; 14,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,41</t>
+          <t>2,6; 9,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,54</t>
+          <t>4,79; 15,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,58</t>
+          <t>4,26; 10,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,23</t>
+          <t>4,66; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,59</t>
+          <t>7,71; 16,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,94</t>
+          <t>0,0; 14,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,26</t>
+          <t>3,11; 13,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 11,25</t>
+          <t>2,15; 12,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,42</t>
+          <t>3,82; 9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,1</t>
+          <t>4,65; 9,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,77</t>
+          <t>6,75; 13,78</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 16,39</t>
+          <t>5,01; 15,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 22,78</t>
+          <t>8,04; 22,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 22,58</t>
+          <t>2,69; 24,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,78</t>
+          <t>1,35; 15,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 27,71</t>
+          <t>7,53; 26,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,31</t>
+          <t>2,02; 11,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,73</t>
+          <t>4,34; 12,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 20,54</t>
+          <t>9,55; 21,01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 21,02</t>
+          <t>2,13; 21,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 20,54</t>
+          <t>2,12; 19,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 15,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 18,13</t>
+          <t>2,15; 19,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 19,28</t>
+          <t>1,89; 18,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,91</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,79</t>
+          <t>5,69; 10,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,9</t>
+          <t>5,88; 9,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,93</t>
+          <t>9,32; 14,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,15</t>
+          <t>5,27; 12,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,69</t>
+          <t>5,52; 11,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,85</t>
+          <t>5,57; 11,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,83</t>
+          <t>5,92; 9,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,51</t>
+          <t>6,41; 9,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,91</t>
+          <t>8,75; 12,81</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4874; 16574</t>
+          <t>4789; 16623</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7108; 22974</t>
+          <t>7345; 22894</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5629; 20013</t>
+          <t>5059; 19118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7135</t>
+          <t>0; 8150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1973; 11300</t>
+          <t>1959; 10650</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1773; 10496</t>
+          <t>1754; 9732</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6795; 19654</t>
+          <t>6767; 20178</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11181; 29515</t>
+          <t>11639; 30759</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8766; 24125</t>
+          <t>8793; 23997</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2604; 13866</t>
+          <t>2700; 13955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3225; 16898</t>
+          <t>3035; 15467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6073; 19559</t>
+          <t>5437; 17865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2192; 12670</t>
+          <t>3109; 13200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2022; 12225</t>
+          <t>2005; 12214</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>985; 9366</t>
+          <t>1003; 9685</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7146; 22571</t>
+          <t>7236; 21859</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8181; 24287</t>
+          <t>7655; 23484</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8271; 25428</t>
+          <t>8364; 24698</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5397; 17629</t>
+          <t>5350; 17320</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2992; 14048</t>
+          <t>3192; 14399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4871; 16347</t>
+          <t>4725; 16246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>0; 5009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7982</t>
+          <t>922; 7803</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5760; 18361</t>
+          <t>5722; 18944</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5248; 18553</t>
+          <t>5127; 17995</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5232; 17327</t>
+          <t>5341; 17060</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11447; 28786</t>
+          <t>11603; 28107</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14502; 32623</t>
+          <t>14870; 33287</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17572; 37791</t>
+          <t>17548; 37686</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8830</t>
+          <t>0; 9133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3961; 15002</t>
+          <t>3519; 14975</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1860; 9751</t>
+          <t>1862; 10487</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13603; 31584</t>
+          <t>12825; 30587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21318; 43638</t>
+          <t>20074; 42027</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21427; 43310</t>
+          <t>21224; 43326</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6136</t>
+          <t>0; 6527</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6467; 20832</t>
+          <t>6364; 19324</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8815; 24533</t>
+          <t>8663; 23731</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>971; 8017</t>
+          <t>956; 8555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>939; 11650</t>
+          <t>938; 10712</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5990; 19452</t>
+          <t>5286; 18654</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2024; 11207</t>
+          <t>2006; 11462</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8947; 25019</t>
+          <t>8531; 25214</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16681; 36538</t>
+          <t>16980; 37380</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1166; 10297</t>
+          <t>1043; 10596</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1275; 12514</t>
+          <t>1293; 11659</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5752</t>
+          <t>0; 5670</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1038; 9881</t>
+          <t>1174; 10623</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1318; 12909</t>
+          <t>1266; 12170</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6635</t>
+          <t>0; 6428</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34141; 61047</t>
+          <t>35513; 62627</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48425; 80815</t>
+          <t>48021; 80630</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58291; 90426</t>
+          <t>56420; 89752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12250; 30475</t>
+          <t>13218; 31847</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21884; 44929</t>
+          <t>21241; 44695</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19026; 39638</t>
+          <t>18627; 39341</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53430; 85936</t>
+          <t>51764; 83503</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>74444; 114147</t>
+          <t>76995; 115735</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81510; 121311</t>
+          <t>82218; 120420</t>
         </is>
       </c>
     </row>
